--- a/data/trans_orig/IP1004-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49137</t>
+          <t>49144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109365</t>
+          <t>109381</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103568</t>
+          <t>105411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206956</t>
+          <t>206967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75269</t>
+          <t>75256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>149586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40623</t>
+          <t>41050</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83147</t>
+          <t>83148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52402</t>
+          <t>52376</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>56610</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111074</t>
+          <t>111060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>676678</t>
+          <t>676774</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>715814</t>
+          <t>714969</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>721513</t>
+          <t>721434</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1394747</t>
+          <t>1394933</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1401803</t>
+          <t>1401718</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56562</t>
+          <t>54869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109460</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67173</t>
+          <t>66218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135005</t>
+          <t>135034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>160730</t>
+          <t>160013</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>166136</t>
+          <t>167429</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331330</t>
+          <t>330526</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>702969</t>
+          <t>701968</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>741068</t>
+          <t>741659</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>747397</t>
+          <t>747393</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1447207</t>
+          <t>1447028</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1454215</t>
+          <t>1454279</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73729</t>
+          <t>73740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39532</t>
+          <t>39332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85652</t>
+          <t>85198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>699095</t>
+          <t>699595</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1444861</t>
+          <t>1444503</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP1004-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3424</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3667</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3449</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51885</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49144</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48901</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,02%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>169</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109381</t>
+          <t>109336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,84 +1065,84 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3346</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108090</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105406</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108090</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>105411</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206967</t>
+          <t>206982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3855</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1266</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4386</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1869,67 +1869,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>77845</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74653</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>77845</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75256</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149586</t>
+          <t>149399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>704</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>704</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3793</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3523</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3547</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44139</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42004</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44139</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>41050</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83148</t>
+          <t>83172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2442,102 +2442,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3094</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3679</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3627</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3122</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4884</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4727</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59114</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56638</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55323</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>52376</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>52428</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>93,53%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59114</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>56610</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>94,77%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>174</t>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111060</t>
+          <t>110903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2893,47 +2893,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3236,47 +3236,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7372</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4247</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4515</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1266</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>7731</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>719445</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>715328</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>721513</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>679606</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>676774</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>676506</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>719445</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>714969</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>721434</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2097</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1394933</t>
+          <t>1394329</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1401718</t>
+          <t>1401992</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,107 +4045,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>857</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>857</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5892</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4249</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3516</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4158,72 +4158,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59904</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56483</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59904</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>54869</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110209</t>
+          <t>109476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4501,47 +4501,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4731,84 +4731,84 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>744</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>744</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4366</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4844,72 +4844,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69840</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66896</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69840</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66218</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135034</t>
+          <t>135023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5187,47 +5187,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5873,47 +5873,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6216,47 +6216,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6451,102 +6451,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4636</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4513</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3886</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5472</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>5497</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -6559,74 +6559,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170538</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>166679</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>163918</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>160013</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>160195</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170538</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>167429</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>496</t>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330526</t>
+          <t>330551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,72 +6789,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6347</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4960</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4559</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>6483</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>853</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>745763</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>741795</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>747397</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>706138</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>701968</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>702369</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,89%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>745763</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>741659</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>747393</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1447028</t>
+          <t>1446790</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1454279</t>
+          <t>1454217</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7824,47 +7824,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8397,72 +8397,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>589</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3221</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2951</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8510,74 +8510,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76372</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73740</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>74010</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,17%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>218</t>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155155</t>
+          <t>155150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8740,107 +8740,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4106</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3825</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -8853,74 +8853,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>42667</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>39332</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>39613</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,22%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>130</t>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85198</t>
+          <t>86259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9539,47 +9539,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9882,47 +9882,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,72 +10112,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4776</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5576</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>703011</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>699595</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>698795</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2124</t>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1444503</t>
+          <t>1444390</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
